--- a/excel/Batch_06_Leads_Tracker.xlsx
+++ b/excel/Batch_06_Leads_Tracker.xlsx
@@ -937,7 +937,7 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H7" t="str">
-        <v>Sent</v>
+        <v>Replied</v>
       </c>
       <c r="I7" t="str">
         <v>2026-09-10</v>

--- a/excel/Batch_06_Leads_Tracker.xlsx
+++ b/excel/Batch_06_Leads_Tracker.xlsx
@@ -2183,7 +2183,7 @@
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
-      <formula1>"Draft,Sent,Replied,Closed"</formula1>
+      <formula1>"Draft,Sent,Replied,Mail Not Found,Bounce Back,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>

--- a/excel/Batch_06_Leads_Tracker.xlsx
+++ b/excel/Batch_06_Leads_Tracker.xlsx
@@ -533,10 +533,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N2" t="str">
         <v>Final check-in about the Top Choice Roofing Ltd website</v>
@@ -618,10 +618,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N3" t="str">
         <v>Final check-in about the Window &amp; Steel Services Ltd website</v>
@@ -703,10 +703,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N4" t="str">
         <v>Final check-in about the Carshalton Electrical Services Ltd website</v>
@@ -873,10 +873,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N6" t="str">
         <v>Final check-in about the Nora's Cleaning Company Ltd website</v>
@@ -1044,10 +1044,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N8" t="str">
         <v>Final check-in about the Chicken &amp; Drinks website</v>
@@ -1129,10 +1129,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N9" t="str">
         <v>Final check-in about the Henry Maintenance and Carpentry website</v>
@@ -1214,10 +1214,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N10" t="str">
         <v>Final check-in about the RSW Design Studio website</v>
@@ -1299,10 +1299,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N11" t="str">
         <v>Final check-in about the Downey Jones Executive Search website</v>
@@ -1384,10 +1384,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N12" t="str">
         <v>Final check-in about the Sherlock London website</v>
@@ -1469,10 +1469,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N13" t="str">
         <v>Final check-in about the The Robert McLoughlin Practice website</v>
@@ -1554,10 +1554,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N14" t="str">
         <v>Final check-in about the Serviced Virtual Offices Ltd website</v>
@@ -1724,10 +1724,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N16" t="str">
         <v>Final check-in about the Goldstein &amp; Lee, P.C. website</v>
@@ -1809,10 +1809,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N17" t="str">
         <v>Final check-in about the North Cleaners website</v>
@@ -1894,10 +1894,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N18" t="str">
         <v>Final check-in about the Access Cleaning and Management Services website</v>
@@ -1979,10 +1979,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N19" t="str">
         <v>Final check-in about the AMR Contractor website</v>
@@ -2064,10 +2064,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N20" t="str">
         <v>Final check-in about the Starbuck Upholstery &amp; Shutters website</v>
@@ -2149,10 +2149,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>2026-09-21</v>
       </c>
       <c r="N21" t="str">
         <v>Final check-in about the Sure Word International Church website</v>

--- a/excel/Batch_06_Leads_Tracker.xlsx
+++ b/excel/Batch_06_Leads_Tracker.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -418,6 +418,7 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,9 @@
       </c>
       <c r="R1" t="str">
         <v>Lead Status</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Notes</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -560,6 +564,9 @@
       <c r="R2" t="str">
         <v/>
       </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -645,6 +652,9 @@
       <c r="R3" t="str">
         <v/>
       </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
@@ -730,6 +740,9 @@
       <c r="R4" t="str">
         <v/>
       </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
@@ -815,6 +828,9 @@
       <c r="R5" t="str">
         <v/>
       </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
@@ -900,6 +916,9 @@
       <c r="R6" t="str">
         <v/>
       </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
@@ -985,6 +1004,9 @@
       <c r="R7" t="str">
         <v/>
       </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
@@ -1071,6 +1093,9 @@
       <c r="R8" t="str">
         <v/>
       </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
@@ -1156,6 +1181,9 @@
       <c r="R9" t="str">
         <v/>
       </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
@@ -1241,6 +1269,9 @@
       <c r="R10" t="str">
         <v/>
       </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
@@ -1326,6 +1357,9 @@
       <c r="R11" t="str">
         <v/>
       </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
@@ -1411,6 +1445,9 @@
       <c r="R12" t="str">
         <v/>
       </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
@@ -1496,6 +1533,9 @@
       <c r="R13" t="str">
         <v/>
       </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
@@ -1581,6 +1621,9 @@
       <c r="R14" t="str">
         <v/>
       </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
@@ -1618,10 +1661,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H15" t="str">
-        <v>Draft</v>
+        <v>Mail Not Found</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2026-10-07</v>
       </c>
       <c r="J15" t="str">
         <v>Following up: Richmond IT Consulting website concept</v>
@@ -1664,6 +1707,9 @@
         <v/>
       </c>
       <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
         <v/>
       </c>
     </row>
@@ -1751,6 +1797,9 @@
       <c r="R16" t="str">
         <v/>
       </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17" t="str">
@@ -1836,6 +1885,9 @@
       <c r="R17" t="str">
         <v/>
       </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
@@ -1921,6 +1973,9 @@
       <c r="R18" t="str">
         <v/>
       </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
@@ -2006,6 +2061,9 @@
       <c r="R19" t="str">
         <v/>
       </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
@@ -2091,6 +2149,9 @@
       <c r="R20" t="str">
         <v/>
       </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21" t="str">
@@ -2176,10 +2237,13 @@
       <c r="R21" t="str">
         <v/>
       </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
